--- a/artfynd/A 37846-2025 artfynd.xlsx
+++ b/artfynd/A 37846-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>73981913</v>
       </c>
       <c r="B2" t="n">
-        <v>106707</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109171</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>496405.5030160605</v>
+        <v>496406</v>
       </c>
       <c r="R2" t="n">
-        <v>6400091.986338146</v>
+        <v>6400092</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1982-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1985-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -804,12 +789,7 @@
         <v>74253404</v>
       </c>
       <c r="B3" t="n">
-        <v>96974</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99263</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496405.5030160605</v>
+        <v>496406</v>
       </c>
       <c r="R3" t="n">
-        <v>6400091.986338146</v>
+        <v>6400092</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -874,19 +854,9 @@
           <t>1982-01-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1985-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -930,12 +900,7 @@
         <v>74573596</v>
       </c>
       <c r="B4" t="n">
-        <v>106757</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109223</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -967,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>496405.5030160605</v>
+        <v>496406</v>
       </c>
       <c r="R4" t="n">
-        <v>6400091.986338146</v>
+        <v>6400092</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1000,19 +965,9 @@
           <t>1982-01-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1985-12-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1056,12 +1011,7 @@
         <v>74566909</v>
       </c>
       <c r="B5" t="n">
-        <v>96356</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98611</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1093,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>496405.5030160605</v>
+        <v>496406</v>
       </c>
       <c r="R5" t="n">
-        <v>6400091.986338146</v>
+        <v>6400092</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1126,19 +1076,9 @@
           <t>1982-01-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>1985-12-31</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">

--- a/artfynd/A 37846-2025 artfynd.xlsx
+++ b/artfynd/A 37846-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73981913</v>
       </c>
       <c r="B2" t="n">
-        <v>109171</v>
+        <v>109180</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74253404</v>
       </c>
       <c r="B3" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74573596</v>
       </c>
       <c r="B4" t="n">
-        <v>109223</v>
+        <v>109232</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74566909</v>
       </c>
       <c r="B5" t="n">
-        <v>98611</v>
+        <v>98614</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37846-2025 artfynd.xlsx
+++ b/artfynd/A 37846-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73981913</v>
       </c>
       <c r="B2" t="n">
-        <v>109180</v>
+        <v>109185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74253404</v>
       </c>
       <c r="B3" t="n">
-        <v>99268</v>
+        <v>99269</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74573596</v>
       </c>
       <c r="B4" t="n">
-        <v>109232</v>
+        <v>109237</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74566909</v>
       </c>
       <c r="B5" t="n">
-        <v>98614</v>
+        <v>98615</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37846-2025 artfynd.xlsx
+++ b/artfynd/A 37846-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73981913</v>
       </c>
       <c r="B2" t="n">
-        <v>109185</v>
+        <v>109213</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74253404</v>
       </c>
       <c r="B3" t="n">
-        <v>99269</v>
+        <v>99296</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74573596</v>
       </c>
       <c r="B4" t="n">
-        <v>109237</v>
+        <v>109265</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74566909</v>
       </c>
       <c r="B5" t="n">
-        <v>98615</v>
+        <v>98642</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37846-2025 artfynd.xlsx
+++ b/artfynd/A 37846-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73981913</v>
       </c>
       <c r="B2" t="n">
-        <v>109213</v>
+        <v>109219</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74253404</v>
       </c>
       <c r="B3" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74573596</v>
       </c>
       <c r="B4" t="n">
-        <v>109265</v>
+        <v>109271</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74566909</v>
       </c>
       <c r="B5" t="n">
-        <v>98642</v>
+        <v>98648</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37846-2025 artfynd.xlsx
+++ b/artfynd/A 37846-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73981913</v>
       </c>
       <c r="B2" t="n">
-        <v>109219</v>
+        <v>109226</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74253404</v>
       </c>
       <c r="B3" t="n">
-        <v>99302</v>
+        <v>99309</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74573596</v>
       </c>
       <c r="B4" t="n">
-        <v>109271</v>
+        <v>109278</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74566909</v>
       </c>
       <c r="B5" t="n">
-        <v>98648</v>
+        <v>98655</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37846-2025 artfynd.xlsx
+++ b/artfynd/A 37846-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73981913</v>
       </c>
       <c r="B2" t="n">
-        <v>109226</v>
+        <v>109230</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74253404</v>
       </c>
       <c r="B3" t="n">
-        <v>99309</v>
+        <v>99313</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74573596</v>
       </c>
       <c r="B4" t="n">
-        <v>109278</v>
+        <v>109282</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74566909</v>
       </c>
       <c r="B5" t="n">
-        <v>98655</v>
+        <v>98659</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37846-2025 artfynd.xlsx
+++ b/artfynd/A 37846-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73981913</v>
       </c>
       <c r="B2" t="n">
-        <v>109230</v>
+        <v>109238</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74253404</v>
       </c>
       <c r="B3" t="n">
-        <v>99313</v>
+        <v>99320</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74573596</v>
       </c>
       <c r="B4" t="n">
-        <v>109282</v>
+        <v>109290</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74566909</v>
       </c>
       <c r="B5" t="n">
-        <v>98659</v>
+        <v>98666</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37846-2025 artfynd.xlsx
+++ b/artfynd/A 37846-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73981913</v>
       </c>
       <c r="B2" t="n">
-        <v>109241</v>
+        <v>109246</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74253404</v>
       </c>
       <c r="B3" t="n">
-        <v>99323</v>
+        <v>99328</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74573596</v>
       </c>
       <c r="B4" t="n">
-        <v>109293</v>
+        <v>109298</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74566909</v>
       </c>
       <c r="B5" t="n">
-        <v>98669</v>
+        <v>98674</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37846-2025 artfynd.xlsx
+++ b/artfynd/A 37846-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73981913</v>
       </c>
       <c r="B2" t="n">
-        <v>109246</v>
+        <v>109254</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74253404</v>
       </c>
       <c r="B3" t="n">
-        <v>99328</v>
+        <v>99336</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74573596</v>
       </c>
       <c r="B4" t="n">
-        <v>109298</v>
+        <v>109306</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74566909</v>
       </c>
       <c r="B5" t="n">
-        <v>98674</v>
+        <v>98682</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37846-2025 artfynd.xlsx
+++ b/artfynd/A 37846-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73981913</v>
       </c>
       <c r="B2" t="n">
-        <v>109254</v>
+        <v>109264</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74253404</v>
       </c>
       <c r="B3" t="n">
-        <v>99336</v>
+        <v>99346</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74573596</v>
       </c>
       <c r="B4" t="n">
-        <v>109306</v>
+        <v>109316</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>74566909</v>
       </c>
       <c r="B5" t="n">
-        <v>98682</v>
+        <v>98692</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37846-2025 artfynd.xlsx
+++ b/artfynd/A 37846-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>73981913</v>
+        <v>74566909</v>
       </c>
       <c r="B2" t="n">
-        <v>109264</v>
+        <v>99142</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220204</v>
+        <v>219847</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -750,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 7E0j 2334. SOM: Hypochoeris maculata. LEG: Bengt-Olof Karlsson</t>
+          <t>Smålands flora 2007: KOO: 7E0j 2334. SOM: Listera ovata. LEG: Bengt-Olof Karlsson</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>74253404</v>
+        <v>73981913</v>
       </c>
       <c r="B3" t="n">
-        <v>99346</v>
+        <v>109814</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222322</v>
+        <v>220204</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -861,7 +861,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 7E0j 2334. SOM: Carex hostiana. LEG: Bengt-Olof Karlsson</t>
+          <t>Smålands flora 2007: KOO: 7E0j 2334. SOM: Hypochoeris maculata. LEG: Bengt-Olof Karlsson</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,7 +900,7 @@
         <v>74573596</v>
       </c>
       <c r="B4" t="n">
-        <v>109316</v>
+        <v>109865</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,32 +1008,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>74566909</v>
+        <v>74253404</v>
       </c>
       <c r="B5" t="n">
-        <v>98692</v>
+        <v>99802</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219847</v>
+        <v>222322</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 7E0j 2334. SOM: Listera ovata. LEG: Bengt-Olof Karlsson</t>
+          <t>Smålands flora 2007: KOO: 7E0j 2334. SOM: Carex hostiana. LEG: Bengt-Olof Karlsson</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 37846-2025 artfynd.xlsx
+++ b/artfynd/A 37846-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74566909</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73981913</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74573596</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,8 +1136,19 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74253404</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>